--- a/Invoice Storage/vinayaka sanitory/INV-20260913-183041-008.xlsx
+++ b/Invoice Storage/vinayaka sanitory/INV-20260913-183041-008.xlsx
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="15" t="n">
         <v>210</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1050</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>33709</v>
+        <v>33499</v>
       </c>
     </row>
     <row r="35">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D36" s="17" t="n">
-        <v>33830</v>
+        <v>33620</v>
       </c>
     </row>
   </sheetData>
